--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487425_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487425_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.895899999999999</v>
+        <v>11.1615</v>
       </c>
       <c r="E2" t="n">
-        <v>7.158</v>
+        <v>8.316599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7379</v>
+        <v>2.8448</v>
       </c>
       <c r="G2" t="n">
         <v>2.5645</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1517</v>
+        <v>2.4172</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1559</v>
+        <v>1.0028</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3076</v>
+        <v>1.4145</v>
       </c>
       <c r="V2" t="n">
         <v>4.8088</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PETERS</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.7235</v>
+        <v>6.5553</v>
       </c>
       <c r="E3" t="n">
-        <v>8.0017</v>
+        <v>4.3598</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2783</v>
+        <v>2.1956</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8376</v>
+        <v>0.3239</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8473</v>
+        <v>-0.7272</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.0512</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9658</v>
+        <v>0.6344</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0014</v>
+        <v>0.0186</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0356</v>
+        <v>0.6159</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1281</v>
+        <v>-0.3105</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1541</v>
+        <v>-0.7458</v>
       </c>
       <c r="O3" t="n">
-        <v>0.026</v>
+        <v>0.4353</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1751</v>
+        <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>4.0241</v>
+        <v>1.8397</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3067</v>
+        <v>1.2921</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7174</v>
+        <v>0.5476</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6659</v>
+        <v>2.4332</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7086</v>
+        <v>2.4332</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0427</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>R. PETERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.5576</v>
+        <v>5.7354</v>
       </c>
       <c r="E4" t="n">
-        <v>5.469</v>
+        <v>6.6284</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0886</v>
+        <v>-0.8931</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3239</v>
+        <v>2.8376</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7272</v>
+        <v>2.8473</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0512</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6344</v>
+        <v>3.9658</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0186</v>
+        <v>4.0014</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6159</v>
+        <v>-0.0356</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3105</v>
+        <v>-1.1281</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7458</v>
+        <v>-1.1541</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4353</v>
+        <v>0.026</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9585</v>
+        <v>1.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>2.842</v>
+        <v>2.036</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4013</v>
+        <v>0.9334</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4406</v>
+        <v>1.1026</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4332</v>
+        <v>0.6659</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4332</v>
+        <v>2.7086</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.0427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8219</v>
+        <v>5.4125</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9345</v>
+        <v>2.4722</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8874</v>
+        <v>2.9403</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7566</v>
+        <v>0.7062</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9876</v>
+        <v>1.3528</v>
       </c>
       <c r="I5" t="n">
-        <v>1.769</v>
+        <v>-0.6466</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3973</v>
+        <v>1.3552</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2761</v>
+        <v>2.71</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1212</v>
+        <v>-1.3548</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3593</v>
+        <v>-0.649</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2884</v>
+        <v>-1.3572</v>
       </c>
       <c r="O5" t="n">
-        <v>1.6477</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5875</v>
+        <v>2.3502</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>2.3502</v>
       </c>
       <c r="S5" t="n">
-        <v>4.9846</v>
+        <v>1.7478</v>
       </c>
       <c r="T5" t="n">
-        <v>3.3147</v>
+        <v>0.5087</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6699</v>
+        <v>1.2391</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3318</v>
+        <v>0.6083</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1602</v>
+        <v>0.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5518</v>
+        <v>4.0793</v>
       </c>
       <c r="E6" t="n">
-        <v>1.066</v>
+        <v>1.4324</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4858</v>
+        <v>2.6469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7062</v>
+        <v>2.7566</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3528</v>
+        <v>0.9876</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6466</v>
+        <v>1.769</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3552</v>
+        <v>2.3973</v>
       </c>
       <c r="K6" t="n">
-        <v>2.71</v>
+        <v>2.2761</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3548</v>
+        <v>0.1212</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.649</v>
+        <v>0.3593</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.3572</v>
+        <v>-1.2884</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7082000000000001</v>
+        <v>1.6477</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3502</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R6" t="n">
         <v>2.3502</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1129</v>
+        <v>3.242</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8975</v>
+        <v>1.8126</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7846</v>
+        <v>1.4293</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6083</v>
+        <v>-1.3318</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6083</v>
+        <v>0.1602</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1501</v>
+        <v>3.9423</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2039</v>
+        <v>0.5883</v>
       </c>
       <c r="F7" t="n">
         <v>3.3541</v>
@@ -1000,10 +1000,10 @@
         <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1894</v>
+        <v>0.6028</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6952</v>
+        <v>0.097</v>
       </c>
       <c r="U7" t="n">
         <v>0.5058</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5036</v>
+        <v>0.6432</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0186</v>
+        <v>0.0408</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5222</v>
+        <v>0.6024</v>
       </c>
       <c r="G8" t="n">
         <v>0.3137</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0059</v>
+        <v>0.1337</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0594</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0019</v>
+        <v>0.3494</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8962</v>
+        <v>-0.3845</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8942</v>
+        <v>0.7338</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3919</v>
@@ -1156,13 +1156,13 @@
         <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1181</v>
+        <v>0.2332</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>0.1553</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2383</v>
+        <v>0.0779</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2754</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9903</v>
+        <v>-0.2566</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9366</v>
+        <v>-0.6087</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0537</v>
+        <v>0.3521</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3083</v>
+        <v>-0.8371</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.101</v>
+        <v>0.3246</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4093</v>
+        <v>-1.1617</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1021</v>
+        <v>-0.2558</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1021</v>
+        <v>1.7505</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-2.0063</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2062</v>
+        <v>-0.5813</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2031</v>
+        <v>-1.4259</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4093</v>
+        <v>0.8446</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1726</v>
+        <v>0.7971</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0594</v>
+        <v>0.6264</v>
       </c>
       <c r="U10" t="n">
-        <v>0.232</v>
+        <v>0.1707</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.8837</v>
+        <v>-0.6083</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.8837</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8427</v>
+        <v>-1.0645</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7938</v>
+        <v>-0.8772</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0489</v>
+        <v>-0.1874</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8371</v>
+        <v>0.3083</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3246</v>
+        <v>-0.101</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1617</v>
+        <v>0.4093</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2558</v>
+        <v>0.1021</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7505</v>
+        <v>0.1021</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0063</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5813</v>
+        <v>0.2062</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4259</v>
+        <v>-0.2031</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8446</v>
+        <v>0.4093</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.789</v>
+        <v>0.0984</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5587</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2302</v>
+        <v>0.0984</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6083</v>
+        <v>-0.8837</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6083</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>35.3695</v>
+        <v>36.5578</v>
       </c>
       <c r="E12" t="n">
-        <v>20.7801</v>
+        <v>21.9681</v>
       </c>
       <c r="F12" t="n">
-        <v>14.5893</v>
+        <v>14.5895</v>
       </c>
       <c r="G12" t="n">
         <v>8.884499999999999</v>
@@ -1372,10 +1372,10 @@
         <v>-4.8795</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.182700000000001</v>
+        <v>-2.1827</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.4786</v>
+        <v>-8.478599999999998</v>
       </c>
       <c r="O12" t="n">
         <v>6.2957</v>
@@ -1390,13 +1390,13 @@
         <v>14.6886</v>
       </c>
       <c r="S12" t="n">
-        <v>11.9597</v>
+        <v>13.1479</v>
       </c>
       <c r="T12" t="n">
-        <v>5.2402</v>
+        <v>6.4283</v>
       </c>
       <c r="U12" t="n">
-        <v>6.719500000000001</v>
+        <v>6.719600000000001</v>
       </c>
       <c r="V12" t="n">
         <v>6.691199999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5289</v>
+        <v>1.8774</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8017</v>
+        <v>3.904</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.2728</v>
+        <v>-2.0267</v>
       </c>
       <c r="G13" t="n">
         <v>1.9276</v>
@@ -1468,13 +1468,13 @@
         <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4723</v>
+        <v>-1.1238</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8269</v>
+        <v>-0.7246</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6454</v>
+        <v>-0.3992</v>
       </c>
       <c r="V13" t="n">
         <v>1.8569</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. CACHON VILLAMEDIANA</t>
+          <t>J. FERNÁNDEZ DEL RÍO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3543</v>
+        <v>-0.4813</v>
       </c>
       <c r="E14" t="n">
-        <v>1.147</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5013</v>
+        <v>-0.5562</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8951</v>
+        <v>0.2476</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9703000000000001</v>
+        <v>-1.8288</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9247</v>
+        <v>2.0764</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9721</v>
+        <v>1.4006</v>
       </c>
       <c r="K14" t="n">
-        <v>3.0077</v>
+        <v>0.1429</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0356</v>
+        <v>1.2577</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.077</v>
+        <v>-1.153</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0373</v>
+        <v>-1.9717</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9603</v>
+        <v>0.8187</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1751</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9792</v>
+        <v>0.5875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8723</v>
+        <v>-0.3372</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9951</v>
+        <v>-0.3464</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1228</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.9466</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2807</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERNÁNDEZ DEL RÍO</t>
+          <t>R. CACHON VILLAMEDIANA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.0584</v>
+        <v>-1.7371</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2321</v>
+        <v>-0.081</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8263</v>
+        <v>-1.6561</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2476</v>
+        <v>1.8951</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.8288</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>2.0764</v>
+        <v>0.9247</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4006</v>
+        <v>2.9721</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1429</v>
+        <v>3.0077</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2577</v>
+        <v>-0.0356</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.153</v>
+        <v>-1.077</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9717</v>
+        <v>-2.0373</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8187</v>
+        <v>0.9603</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3917</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5875</v>
+        <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9143</v>
+        <v>-0.5105</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6534</v>
+        <v>-0.2329</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2608</v>
+        <v>-0.2776</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.9466</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.2807</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.2762</v>
+        <v>-2.6383</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4073</v>
+        <v>-1.2026</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.869</v>
+        <v>-1.4357</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7658</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.1662</v>
+        <v>-1.5283</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.408</v>
+        <v>-1.2033</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7582</v>
+        <v>-0.3249</v>
       </c>
       <c r="V16" t="n">
         <v>0.2433</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.9132</v>
+        <v>-3.8164</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2673</v>
+        <v>-1.5743</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.6459</v>
+        <v>-2.2422</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9124</v>
@@ -1780,13 +1780,13 @@
         <v>0.5875</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0275</v>
+        <v>-0.9307</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.31</v>
+        <v>-0.617</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7175</v>
+        <v>-0.3138</v>
       </c>
       <c r="V17" t="n">
         <v>-1.5816</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-5.8208</v>
+        <v>-5.6401</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.563</v>
+        <v>-2.3584</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.2578</v>
+        <v>-3.2817</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7166</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7298</v>
+        <v>-0.549</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3982</v>
+        <v>-0.1935</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3316</v>
+        <v>-0.3555</v>
       </c>
       <c r="V18" t="n">
         <v>-3.9828</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-6.0781</v>
+        <v>-6.0384</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.9073</v>
+        <v>-4.0096</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1709</v>
+        <v>-2.0288</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4749</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6021</v>
+        <v>-1.5624</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9634</v>
+        <v>-1.0657</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6387</v>
+        <v>-0.4967</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8260999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-7.0051</v>
+        <v>-6.109</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.6649</v>
+        <v>-4.2556</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3402</v>
+        <v>-1.8535</v>
       </c>
       <c r="G20" t="n">
         <v>-4.863</v>
@@ -2014,13 +2014,13 @@
         <v>0.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.564</v>
+        <v>-1.668</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.7644</v>
+        <v>-1.3551</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7996</v>
+        <v>-0.3129</v>
       </c>
       <c r="V20" t="n">
         <v>1.7929</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.392300000000001</v>
+        <v>-8.739599999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.4963</v>
+        <v>-5.0869</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.896</v>
+        <v>-3.6527</v>
       </c>
       <c r="G21" t="n">
         <v>-3.2221</v>
@@ -2092,13 +2092,13 @@
         <v>0.5875</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.356</v>
+        <v>-1.7032</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3904</v>
+        <v>-0.981</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9656</v>
+        <v>-0.7222</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2475</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-35.3695</v>
+        <v>-33.3228</v>
       </c>
       <c r="E22" t="n">
         <v>-14.5895</v>
       </c>
       <c r="F22" t="n">
-        <v>-20.7802</v>
+        <v>-18.7336</v>
       </c>
       <c r="G22" t="n">
         <v>-8.884500000000001</v>
@@ -2140,7 +2140,7 @@
         <v>-7.4682</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.4163</v>
+        <v>-1.416300000000001</v>
       </c>
       <c r="J22" t="n">
         <v>2.1827</v>
@@ -2158,7 +2158,7 @@
         <v>-15.9467</v>
       </c>
       <c r="O22" t="n">
-        <v>4.8796</v>
+        <v>4.879600000000001</v>
       </c>
       <c r="P22" t="n">
         <v>-7.8339</v>
@@ -2170,13 +2170,13 @@
         <v>6.8544</v>
       </c>
       <c r="S22" t="n">
-        <v>-11.9599</v>
+        <v>-9.9131</v>
       </c>
       <c r="T22" t="n">
-        <v>-6.7196</v>
+        <v>-6.7195</v>
       </c>
       <c r="U22" t="n">
-        <v>-5.2402</v>
+        <v>-3.1935</v>
       </c>
       <c r="V22" t="n">
         <v>-6.6915</v>
